--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.15541666371923</v>
+        <v>2.300255207854375</v>
       </c>
       <c r="D2" t="n">
-        <v>14.00909777822094</v>
+        <v>2.276478388960902</v>
       </c>
       <c r="E2" t="n">
-        <v>13.25938640776185</v>
+        <v>2.154650291261301</v>
       </c>
       <c r="F2" t="n">
-        <v>13.51732982425546</v>
+        <v>2.196566096441513</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.67418947924293</v>
+        <v>6.609555790376977</v>
       </c>
       <c r="D3" t="n">
-        <v>41.04375742673187</v>
+        <v>6.669610581843928</v>
       </c>
       <c r="E3" t="n">
-        <v>13.25938640776185</v>
+        <v>2.154650291261301</v>
       </c>
       <c r="F3" t="n">
-        <v>13.51732982425546</v>
+        <v>2.196566096441513</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
